--- a/old/_260807_230418_100sekund-0528.xlsx
+++ b/old/_260807_230418_100sekund-0528.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\old\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61233F71-5738-4491-AFFF-27E01DF52D12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B34F6134-BCE0-4584-ADEF-F410A25BBB82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9980" yWindow="2900" windowWidth="15030" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13010" yWindow="4080" windowWidth="15030" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -217,35 +217,36 @@
     <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
+    <t xml:space="preserve"> Trägt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vermeintlichen</t>
+  </si>
+  <si>
+    <t>wir verunsichert sind</t>
+  </si>
+  <si>
+    <t>gut ausstatten und dafür sorgen, dass</t>
+  </si>
+  <si>
+    <t>in München, in Alarmbereitschaft</t>
+  </si>
+  <si>
+    <t>guter Einfall war</t>
+  </si>
+  <si>
+    <t>Es gibt aber andererseits</t>
+  </si>
+  <si>
+    <t>Hause nicht mehr</t>
+  </si>
+  <si>
+    <t>sonst gehen die nämlich zu Siemens</t>
+  </si>
+  <si>
     <t>Gefährdung</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Trägt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>vermeintlichen</t>
-  </si>
-  <si>
-    <t>wir verunsichert sind</t>
-  </si>
-  <si>
-    <t>gut ausstatten und dafür sorgen, dass</t>
-  </si>
-  <si>
-    <t>in München, in Alarmbereitschaft</t>
-  </si>
-  <si>
-    <t>guter Einfall war</t>
-  </si>
-  <si>
-    <t>Es gibt aber andererseits</t>
-  </si>
-  <si>
-    <t>Hause nicht mehr</t>
-  </si>
-  <si>
-    <t>sonst gehen die nämlich zu Siemens</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -853,52 +854,52 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="36" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="36" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
